--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487490_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487490_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>17.706</v>
+        <v>18.0589</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2791</v>
+        <v>16.9261</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4269</v>
+        <v>1.1328</v>
       </c>
       <c r="G2" t="n">
         <v>8.511200000000001</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0853</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1416</v>
+        <v>-0.4946</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0563</v>
+        <v>-0.2377</v>
       </c>
       <c r="V2" t="n">
         <v>8.1257</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>R. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6096</v>
+        <v>1.5225</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2675</v>
+        <v>-0.9878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3421</v>
+        <v>2.5103</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4325</v>
+        <v>0.39</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1537</v>
+        <v>0.8853</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5862</v>
+        <v>-0.4954</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4169</v>
+        <v>-0.712</v>
       </c>
       <c r="K3" t="n">
-        <v>0.114</v>
+        <v>0.6073</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3029</v>
+        <v>-1.3192</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0156</v>
+        <v>1.102</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2677</v>
+        <v>0.2781</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2833</v>
+        <v>0.8239</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1719</v>
+        <v>-0.1589</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1494</v>
+        <v>-0.2758</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0225</v>
+        <v>0.1169</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANTORUM OTERO</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5678</v>
+        <v>1.3946</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.595</v>
+        <v>1.0793</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1628</v>
+        <v>0.3154</v>
       </c>
       <c r="G4" t="n">
-        <v>0.39</v>
+        <v>1.4325</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8853</v>
+        <v>-0.1537</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4954</v>
+        <v>1.5862</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.712</v>
+        <v>1.4169</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6073</v>
+        <v>0.114</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3192</v>
+        <v>1.3029</v>
       </c>
       <c r="M4" t="n">
-        <v>1.102</v>
+        <v>0.0156</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2781</v>
+        <v>-0.2677</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8239</v>
+        <v>0.2833</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1136</v>
+        <v>-0.3868</v>
       </c>
       <c r="T4" t="n">
-        <v>0.117</v>
+        <v>-0.3376</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2306</v>
+        <v>-0.0493</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5537</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1829</v>
+        <v>-1.3117</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7852</v>
+        <v>1.8654</v>
       </c>
       <c r="G5" t="n">
         <v>1.297</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0887</v>
+        <v>0.0401</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3129</v>
+        <v>0.1841</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2241</v>
+        <v>-0.1439</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>B. LOPEZ CAMIÑA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5957</v>
+        <v>-0.6206</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8174</v>
+        <v>-1.4036</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2217</v>
+        <v>0.7829</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0546</v>
+        <v>-0.5584</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2031</v>
+        <v>-0.6641</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2577</v>
+        <v>0.1057</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2225</v>
+        <v>-0.6314</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3385</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.713</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2771</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5416</v>
+        <v>-0.7458</v>
       </c>
       <c r="O6" t="n">
         <v>0.8187</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9256</v>
+        <v>-1.0414</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.891</v>
+        <v>-0.7722</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0346</v>
+        <v>-0.2692</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6649</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9978</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3864</v>
+        <v>0.3329</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2258</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.202</v>
+        <v>0.1485</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2614</v>
+        <v>0.2079</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. LOPEZ CAMIÑA</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6533</v>
+        <v>-0.6967</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.463</v>
+        <v>-1.758</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8097</v>
+        <v>1.0613</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5584</v>
+        <v>0.0546</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6641</v>
+        <v>-0.2031</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1057</v>
+        <v>0.2577</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6314</v>
+        <v>-0.2225</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.3385</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.713</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2771</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7458</v>
+        <v>-0.5416</v>
       </c>
       <c r="O8" t="n">
         <v>0.8187</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0741</v>
+        <v>-1.0266</v>
       </c>
       <c r="T8" t="n">
         <v>-0.8316</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2425</v>
+        <v>-0.195</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0322</v>
+        <v>-2.3307</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3768</v>
+        <v>-4.5417</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3446</v>
+        <v>2.2109</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4355</v>
@@ -1156,13 +1156,13 @@
         <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2995</v>
+        <v>-0.598</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4674</v>
+        <v>-0.6323</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1679</v>
+        <v>0.0343</v>
       </c>
       <c r="V9" t="n">
         <v>0.1152</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2675</v>
+        <v>-3.3815</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6977</v>
+        <v>-2.9453</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5698</v>
+        <v>-0.4361</v>
       </c>
       <c r="G10" t="n">
         <v>-0.822</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4455</v>
+        <v>-0.5595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4464</v>
+        <v>-0.694</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0009</v>
+        <v>0.1345</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.282</v>
+        <v>-4.3783</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7362</v>
+        <v>-2.7791</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5458</v>
+        <v>-1.5992</v>
       </c>
       <c r="G11" t="n">
         <v>1.6161</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.095</v>
+        <v>-0.1914</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1317</v>
+        <v>-0.1747</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0367</v>
+        <v>-0.0168</v>
       </c>
       <c r="V11" t="n">
         <v>-4.0403</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0349</v>
+        <v>-5.2602</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3998</v>
+        <v>-5.8123</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3649</v>
+        <v>0.5521</v>
       </c>
       <c r="G12" t="n">
         <v>-5.2336</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9557</v>
+        <v>-0.181</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6664</v>
+        <v>-0.0788</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2893</v>
+        <v>-0.1022</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2166</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.008699999999999</v>
+        <v>4.196800000000004</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.720000000000004</v>
+        <v>-4.531899999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>8.728699999999998</v>
+        <v>8.7287</v>
       </c>
       <c r="G13" t="n">
-        <v>4.026099999999999</v>
+        <v>4.026100000000002</v>
       </c>
       <c r="H13" t="n">
         <v>6.8328</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.8068</v>
+        <v>-2.806800000000001</v>
       </c>
       <c r="J13" t="n">
         <v>1.4744</v>
@@ -1453,7 +1453,7 @@
         <v>2.551500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2812999999999999</v>
+        <v>-0.2813</v>
       </c>
       <c r="O13" t="n">
         <v>2.832799999999999</v>
@@ -1468,13 +1468,13 @@
         <v>13.7093</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.8755</v>
+        <v>-4.6874</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.355</v>
+        <v>-4.1669</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5204</v>
+        <v>-0.5204999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.9412999999999998</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.2277</v>
+        <v>6.4575</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9584</v>
+        <v>5.014</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2693</v>
+        <v>1.4434</v>
       </c>
       <c r="G14" t="n">
         <v>2.0996</v>
@@ -1546,13 +1546,13 @@
         <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1281</v>
+        <v>2.3578</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9054</v>
+        <v>0.961</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2227</v>
+        <v>1.3968</v>
       </c>
       <c r="V14" t="n">
         <v>1.2166</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7976</v>
+        <v>2.2983</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.8925</v>
+        <v>-1.0738</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6901</v>
+        <v>3.3721</v>
       </c>
       <c r="G15" t="n">
         <v>2.8136</v>
@@ -1624,13 +1624,13 @@
         <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5769</v>
+        <v>1.0776</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9634</v>
+        <v>-0.1447</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5403</v>
+        <v>1.2223</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0053</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4005</v>
+        <v>0.0554</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0169</v>
+        <v>-1.552</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4175</v>
+        <v>1.6074</v>
       </c>
       <c r="G16" t="n">
         <v>2.1423</v>
@@ -1702,13 +1702,13 @@
         <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3521</v>
+        <v>2.007</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4478</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9043</v>
+        <v>1.0942</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9603</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6083</v>
+        <v>-0.4231</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.5863</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6083</v>
+        <v>-1.0094</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.6975</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1.3236</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.0211</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.2173</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.6466</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8639</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.5198</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.677</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.1572</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6083</v>
+        <v>-1.2807</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6083</v>
+        <v>-1.556</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1356</v>
+        <v>-0.6083</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3817</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5173</v>
+        <v>-0.6083</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6975</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3236</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0211</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2173</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6466</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8639</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5198</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.677</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1572</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3566</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1317</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2248</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2807</v>
+        <v>-0.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.556</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BUENO DE LA ROSA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6128</v>
+        <v>-0.9503</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8586</v>
+        <v>-3.1742</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7542</v>
+        <v>2.224</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8324</v>
+        <v>-2.9915</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3471</v>
+        <v>-2.7802</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4853</v>
+        <v>-0.2113</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.621</v>
+        <v>-2.5591</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0612</v>
+        <v>-1.3563</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6822</v>
+        <v>-1.2028</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2114</v>
+        <v>-0.4324</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4083</v>
+        <v>-1.4239</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8031</v>
+        <v>0.9915</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3502</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0238</v>
+        <v>0.2597</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2376</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2614</v>
+        <v>0.9578</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.3691</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.0641</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>J. BUENO DE LA ROSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5866</v>
+        <v>-1.5639</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2999</v>
+        <v>-0.7563</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7133</v>
+        <v>-0.8077</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9915</v>
+        <v>-1.8324</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7802</v>
+        <v>-0.3471</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2113</v>
+        <v>-1.4853</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5591</v>
+        <v>-0.621</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3563</v>
+        <v>0.0612</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2028</v>
+        <v>-0.6822</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4324</v>
+        <v>-1.2114</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4239</v>
+        <v>-0.4083</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9915</v>
+        <v>-0.8031</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3502</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3767</v>
+        <v>0.0726</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8238</v>
+        <v>-0.1353</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4471</v>
+        <v>0.2079</v>
       </c>
       <c r="V20" t="n">
-        <v>2.3691</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7293</v>
+        <v>-2.5781</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7777</v>
+        <v>-1.573</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9516</v>
+        <v>-1.0051</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9502</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2491</v>
+        <v>-0.0979</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.594</v>
+        <v>-0.3893</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3449</v>
+        <v>0.2914</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5507</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7619</v>
+        <v>-5.014</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.8891</v>
+        <v>-6.8657</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1272</v>
+        <v>1.8517</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0048</v>
@@ -2170,13 +2170,13 @@
         <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.223</v>
+        <v>0.5249</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0822</v>
+        <v>-0.0588</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1408</v>
+        <v>0.5837</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1217</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.008699999999998</v>
+        <v>-2.326500000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.394600000000001</v>
+        <v>-9.3947</v>
       </c>
       <c r="F23" t="n">
-        <v>6.386</v>
+        <v>7.0681</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0259</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.832800000000001</v>
+        <v>-6.8328</v>
       </c>
       <c r="I23" t="n">
         <v>2.806899999999999</v>
@@ -2224,10 +2224,10 @@
         <v>-2.5514</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2812000000000006</v>
+        <v>0.2812000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.832700000000001</v>
+        <v>-2.8327</v>
       </c>
       <c r="M23" t="n">
         <v>-1.4744</v>
@@ -2236,7 +2236,7 @@
         <v>-7.114100000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>5.639600000000001</v>
+        <v>5.6396</v>
       </c>
       <c r="P23" t="n">
         <v>-3.9169</v>
@@ -2248,16 +2248,16 @@
         <v>9.792300000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>5.875500000000001</v>
+        <v>6.5577</v>
       </c>
       <c r="T23" t="n">
         <v>0.5205</v>
       </c>
       <c r="U23" t="n">
-        <v>5.3551</v>
+        <v>6.037100000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9413000000000001</v>
+        <v>-0.9412999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>6.345899999999999</v>
